--- a/data/seo_80kw_production_management_v2_with_image_prompt_sheet.xlsx
+++ b/data/seo_80kw_production_management_v2_with_image_prompt_sheet.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ダッシュボード" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="制作管理表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="アイキャッチ制作指示" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事制作ルール" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="投稿結果ログ" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claude連携メモ" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="旧管理表バックアップ" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画像生成共通プロンプト" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画像生成プロンプト一覧" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="ダッシュボード" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="制作管理表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="アイキャッチ制作指示" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="記事制作ルール" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="設定" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="投稿結果ログ" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Claude連携メモ" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="旧管理表バックアップ" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="画像生成共通プロンプト" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="画像生成プロンプト一覧" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -662,14 +662,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:r>
               <a:rPr/>
               <a:t>ロット別 進捗</a:t>
@@ -692,7 +692,7 @@
             <v>#NAME?</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -721,7 +721,7 @@
             <v>#NAME?</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -750,7 +750,7 @@
             <v>#NAME?</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -779,7 +779,7 @@
             <v>#NAME?</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -823,7 +823,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="CCCCCC"/>
               </a:solidFill>
@@ -850,7 +850,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="CCCCCC"/>
               </a:solidFill>
@@ -874,7 +874,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+    <a:ln w="9525">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -885,7 +885,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>8</col>
@@ -905,9 +905,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -16372,7 +16372,7 @@
       </c>
       <c r="AD2" s="15" t="inlineStr">
         <is>
-          <t>差替必要</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE2" s="15" t="inlineStr">
@@ -16382,24 +16382,37 @@
       </c>
       <c r="AF2" s="15" t="inlineStr">
         <is>
-          <t>要更新確認</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG2" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH2" s="15" t="str"/>
-      <c r="AI2" s="15" t="str"/>
-      <c r="AJ2" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH2" s="15" t="n">
+        <v>21835</v>
+      </c>
+      <c r="AI2" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21835</t>
+        </is>
+      </c>
+      <c r="AJ2" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 16:07:04</t>
+        </is>
+      </c>
       <c r="AK2" s="69" t="str"/>
-      <c r="AL2" s="15" t="str"/>
-      <c r="AM2" s="15">
-        <f>IF(AL2="","",IF(AL2&lt;I2,"不足",IF(AL2&gt;J2,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN2" s="15" t="str"/>
+      <c r="AL2" s="15" t="n">
+        <v>4011</v>
+      </c>
+      <c r="AM2" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,500字)</t>
+        </is>
+      </c>
+      <c r="AN2" s="15" t="inlineStr"/>
       <c r="AO2" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の雨漏り修理」へリンク。関連：雨漏り費用・調査・屋根雨漏り。</t>

--- a/data/seo_80kw_production_management_v2_with_image_prompt_sheet.xlsx
+++ b/data/seo_80kw_production_management_v2_with_image_prompt_sheet.xlsx
@@ -16567,7 +16567,7 @@
       </c>
       <c r="AD3" s="15" t="inlineStr">
         <is>
-          <t>差替必要</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE3" s="15" t="inlineStr">
@@ -16577,24 +16577,37 @@
       </c>
       <c r="AF3" s="15" t="inlineStr">
         <is>
-          <t>要更新確認</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG3" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH3" s="15" t="str"/>
-      <c r="AI3" s="15" t="str"/>
-      <c r="AJ3" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH3" s="15" t="n">
+        <v>21839</v>
+      </c>
+      <c r="AI3" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21839</t>
+        </is>
+      </c>
+      <c r="AJ3" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 16:21:10</t>
+        </is>
+      </c>
       <c r="AK3" s="69" t="str"/>
-      <c r="AL3" s="15" t="str"/>
-      <c r="AM3" s="15">
-        <f>IF(AL3="","",IF(AL3&lt;I3,"不足",IF(AL3&gt;J3,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN3" s="15" t="str"/>
+      <c r="AL3" s="15" t="n">
+        <v>4128</v>
+      </c>
+      <c r="AM3" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,500字)</t>
+        </is>
+      </c>
+      <c r="AN3" s="15" t="inlineStr"/>
       <c r="AO3" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の雨漏り修理」へリンク。関連：雨漏り費用・調査・屋根雨漏り。</t>
@@ -16749,7 +16762,7 @@
       </c>
       <c r="AD4" s="15" t="inlineStr">
         <is>
-          <t>差替必要</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE4" s="15" t="inlineStr">
@@ -16759,24 +16772,37 @@
       </c>
       <c r="AF4" s="15" t="inlineStr">
         <is>
-          <t>要更新確認</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG4" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH4" s="15" t="str"/>
-      <c r="AI4" s="15" t="str"/>
-      <c r="AJ4" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH4" s="15" t="n">
+        <v>21841</v>
+      </c>
+      <c r="AI4" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21841</t>
+        </is>
+      </c>
+      <c r="AJ4" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 16:21:18</t>
+        </is>
+      </c>
       <c r="AK4" s="69" t="str"/>
-      <c r="AL4" s="15" t="str"/>
-      <c r="AM4" s="15">
-        <f>IF(AL4="","",IF(AL4&lt;I4,"不足",IF(AL4&gt;J4,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN4" s="15" t="str"/>
+      <c r="AL4" s="15" t="n">
+        <v>4029</v>
+      </c>
+      <c r="AM4" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,500字)</t>
+        </is>
+      </c>
+      <c r="AN4" s="15" t="inlineStr"/>
       <c r="AO4" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の雨漏り修理」へリンク。関連：雨漏り費用・調査・屋根雨漏り。</t>
@@ -16931,7 +16957,7 @@
       </c>
       <c r="AD5" s="15" t="inlineStr">
         <is>
-          <t>差替必要</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE5" s="15" t="inlineStr">
@@ -16941,24 +16967,37 @@
       </c>
       <c r="AF5" s="15" t="inlineStr">
         <is>
-          <t>要更新確認</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG5" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH5" s="15" t="str"/>
-      <c r="AI5" s="15" t="str"/>
-      <c r="AJ5" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH5" s="15" t="n">
+        <v>21843</v>
+      </c>
+      <c r="AI5" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21843</t>
+        </is>
+      </c>
+      <c r="AJ5" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 16:21:27</t>
+        </is>
+      </c>
       <c r="AK5" s="69" t="str"/>
-      <c r="AL5" s="15" t="str"/>
-      <c r="AM5" s="15">
-        <f>IF(AL5="","",IF(AL5&lt;I5,"不足",IF(AL5&gt;J5,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN5" s="15" t="str"/>
+      <c r="AL5" s="15" t="n">
+        <v>4587</v>
+      </c>
+      <c r="AM5" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN5" s="15" t="inlineStr"/>
       <c r="AO5" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の雨漏り修理」へリンク。関連：雨漏り費用・調査・屋根雨漏り。</t>
@@ -17113,7 +17152,7 @@
       </c>
       <c r="AD6" s="15" t="inlineStr">
         <is>
-          <t>差替必要</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE6" s="15" t="inlineStr">
@@ -17123,24 +17162,37 @@
       </c>
       <c r="AF6" s="15" t="inlineStr">
         <is>
-          <t>要更新確認</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG6" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH6" s="15" t="str"/>
-      <c r="AI6" s="15" t="str"/>
-      <c r="AJ6" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH6" s="15" t="n">
+        <v>21845</v>
+      </c>
+      <c r="AI6" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21845</t>
+        </is>
+      </c>
+      <c r="AJ6" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 16:21:37</t>
+        </is>
+      </c>
       <c r="AK6" s="69" t="str"/>
-      <c r="AL6" s="15" t="str"/>
-      <c r="AM6" s="15">
-        <f>IF(AL6="","",IF(AL6&lt;I6,"不足",IF(AL6&gt;J6,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN6" s="15" t="str"/>
+      <c r="AL6" s="15" t="n">
+        <v>4551</v>
+      </c>
+      <c r="AM6" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN6" s="15" t="inlineStr"/>
       <c r="AO6" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の雨漏り修理」へリンク。関連：雨漏り費用・調査・屋根雨漏り。</t>

--- a/data/seo_80kw_production_management_v2_with_image_prompt_sheet.xlsx
+++ b/data/seo_80kw_production_management_v2_with_image_prompt_sheet.xlsx
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AD7" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE7" s="15" t="inlineStr">
@@ -17357,24 +17357,37 @@
       </c>
       <c r="AF7" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG7" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH7" s="15" t="str"/>
-      <c r="AI7" s="15" t="str"/>
-      <c r="AJ7" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH7" s="15" t="n">
+        <v>21849</v>
+      </c>
+      <c r="AI7" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21849</t>
+        </is>
+      </c>
+      <c r="AJ7" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 16:26:49</t>
+        </is>
+      </c>
       <c r="AK7" s="69" t="str"/>
-      <c r="AL7" s="15" t="str"/>
-      <c r="AM7" s="15">
-        <f>IF(AL7="","",IF(AL7&lt;I7,"不足",IF(AL7&gt;J7,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN7" s="15" t="str"/>
+      <c r="AL7" s="15" t="n">
+        <v>4011</v>
+      </c>
+      <c r="AM7" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,500字)</t>
+        </is>
+      </c>
+      <c r="AN7" s="15" t="inlineStr"/>
       <c r="AO7" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の雨漏り修理」へリンク。関連：雨漏り費用・調査・屋根雨漏り。</t>
@@ -17529,7 +17542,7 @@
       </c>
       <c r="AD8" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE8" s="15" t="inlineStr">
@@ -17539,24 +17552,37 @@
       </c>
       <c r="AF8" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG8" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH8" s="15" t="str"/>
-      <c r="AI8" s="15" t="str"/>
-      <c r="AJ8" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH8" s="15" t="n">
+        <v>21851</v>
+      </c>
+      <c r="AI8" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21851</t>
+        </is>
+      </c>
+      <c r="AJ8" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 16:26:58</t>
+        </is>
+      </c>
       <c r="AK8" s="69" t="str"/>
-      <c r="AL8" s="15" t="str"/>
-      <c r="AM8" s="15">
-        <f>IF(AL8="","",IF(AL8&lt;I8,"不足",IF(AL8&gt;J8,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN8" s="15" t="str"/>
+      <c r="AL8" s="15" t="n">
+        <v>4009</v>
+      </c>
+      <c r="AM8" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,500字)</t>
+        </is>
+      </c>
+      <c r="AN8" s="15" t="inlineStr"/>
       <c r="AO8" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の雨漏り修理」へリンク。関連：雨漏り費用・調査・屋根雨漏り。</t>
@@ -17711,7 +17737,7 @@
       </c>
       <c r="AD9" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE9" s="15" t="inlineStr">
@@ -17721,24 +17747,37 @@
       </c>
       <c r="AF9" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG9" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH9" s="15" t="str"/>
-      <c r="AI9" s="15" t="str"/>
-      <c r="AJ9" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH9" s="15" t="n">
+        <v>21853</v>
+      </c>
+      <c r="AI9" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21853</t>
+        </is>
+      </c>
+      <c r="AJ9" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 16:27:08</t>
+        </is>
+      </c>
       <c r="AK9" s="69" t="str"/>
-      <c r="AL9" s="15" t="str"/>
-      <c r="AM9" s="15">
-        <f>IF(AL9="","",IF(AL9&lt;I9,"不足",IF(AL9&gt;J9,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN9" s="15" t="str"/>
+      <c r="AL9" s="15" t="n">
+        <v>3998</v>
+      </c>
+      <c r="AM9" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,500字)</t>
+        </is>
+      </c>
+      <c r="AN9" s="15" t="inlineStr"/>
       <c r="AO9" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の雨漏り修理」へリンク。関連：雨漏り費用・調査・屋根雨漏り。</t>
@@ -17893,7 +17932,7 @@
       </c>
       <c r="AD10" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE10" s="15" t="inlineStr">
@@ -17903,24 +17942,37 @@
       </c>
       <c r="AF10" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG10" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH10" s="15" t="str"/>
-      <c r="AI10" s="15" t="str"/>
-      <c r="AJ10" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH10" s="15" t="n">
+        <v>21855</v>
+      </c>
+      <c r="AI10" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21855</t>
+        </is>
+      </c>
+      <c r="AJ10" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 16:27:16</t>
+        </is>
+      </c>
       <c r="AK10" s="69" t="str"/>
-      <c r="AL10" s="15" t="str"/>
-      <c r="AM10" s="15">
-        <f>IF(AL10="","",IF(AL10&lt;I10,"不足",IF(AL10&gt;J10,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN10" s="15" t="str"/>
+      <c r="AL10" s="15" t="n">
+        <v>3981</v>
+      </c>
+      <c r="AM10" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,500字)</t>
+        </is>
+      </c>
+      <c r="AN10" s="15" t="inlineStr"/>
       <c r="AO10" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の雨漏り修理」へリンク。関連：雨漏り費用・調査・屋根雨漏り。</t>
@@ -18075,7 +18127,7 @@
       </c>
       <c r="AD11" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE11" s="15" t="inlineStr">
@@ -18085,24 +18137,37 @@
       </c>
       <c r="AF11" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG11" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH11" s="15" t="str"/>
-      <c r="AI11" s="15" t="str"/>
-      <c r="AJ11" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH11" s="15" t="n">
+        <v>21857</v>
+      </c>
+      <c r="AI11" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21857</t>
+        </is>
+      </c>
+      <c r="AJ11" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 16:27:24</t>
+        </is>
+      </c>
       <c r="AK11" s="69" t="str"/>
-      <c r="AL11" s="15" t="str"/>
-      <c r="AM11" s="15">
-        <f>IF(AL11="","",IF(AL11&lt;I11,"不足",IF(AL11&gt;J11,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN11" s="15" t="str"/>
+      <c r="AL11" s="15" t="n">
+        <v>3914</v>
+      </c>
+      <c r="AM11" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,500字)</t>
+        </is>
+      </c>
+      <c r="AN11" s="15" t="inlineStr"/>
       <c r="AO11" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の雨漏り修理」へリンク。関連：雨漏り費用・調査・屋根雨漏り。</t>

--- a/data/seo_80kw_production_management_v2_with_image_prompt_sheet.xlsx
+++ b/data/seo_80kw_production_management_v2_with_image_prompt_sheet.xlsx
@@ -16391,16 +16391,16 @@
         </is>
       </c>
       <c r="AH2" s="15" t="n">
-        <v>21835</v>
+        <v>21921</v>
       </c>
       <c r="AI2" s="15" t="inlineStr">
         <is>
-          <t>https://www.sunadatosou.com/?p=21835</t>
+          <t>https://www.sunadatosou.com/?p=21921</t>
         </is>
       </c>
       <c r="AJ2" s="69" t="inlineStr">
         <is>
-          <t>2026-06-27 16:07:04</t>
+          <t>2026-06-27 16:59:20</t>
         </is>
       </c>
       <c r="AK2" s="69" t="str"/>
@@ -16586,21 +16586,21 @@
         </is>
       </c>
       <c r="AH3" s="15" t="n">
-        <v>21839</v>
+        <v>21923</v>
       </c>
       <c r="AI3" s="15" t="inlineStr">
         <is>
-          <t>https://www.sunadatosou.com/?p=21839</t>
+          <t>https://www.sunadatosou.com/?p=21923</t>
         </is>
       </c>
       <c r="AJ3" s="69" t="inlineStr">
         <is>
-          <t>2026-06-27 16:21:10</t>
+          <t>2026-06-27 16:59:29</t>
         </is>
       </c>
       <c r="AK3" s="69" t="str"/>
       <c r="AL3" s="15" t="n">
-        <v>4128</v>
+        <v>4123</v>
       </c>
       <c r="AM3" s="15" t="inlineStr">
         <is>
@@ -16781,21 +16781,21 @@
         </is>
       </c>
       <c r="AH4" s="15" t="n">
-        <v>21841</v>
+        <v>21925</v>
       </c>
       <c r="AI4" s="15" t="inlineStr">
         <is>
-          <t>https://www.sunadatosou.com/?p=21841</t>
+          <t>https://www.sunadatosou.com/?p=21925</t>
         </is>
       </c>
       <c r="AJ4" s="69" t="inlineStr">
         <is>
-          <t>2026-06-27 16:21:18</t>
+          <t>2026-06-27 16:59:37</t>
         </is>
       </c>
       <c r="AK4" s="69" t="str"/>
       <c r="AL4" s="15" t="n">
-        <v>4029</v>
+        <v>4024</v>
       </c>
       <c r="AM4" s="15" t="inlineStr">
         <is>
@@ -16976,21 +16976,21 @@
         </is>
       </c>
       <c r="AH5" s="15" t="n">
-        <v>21843</v>
+        <v>21927</v>
       </c>
       <c r="AI5" s="15" t="inlineStr">
         <is>
-          <t>https://www.sunadatosou.com/?p=21843</t>
+          <t>https://www.sunadatosou.com/?p=21927</t>
         </is>
       </c>
       <c r="AJ5" s="69" t="inlineStr">
         <is>
-          <t>2026-06-27 16:21:27</t>
+          <t>2026-06-27 16:59:46</t>
         </is>
       </c>
       <c r="AK5" s="69" t="str"/>
       <c r="AL5" s="15" t="n">
-        <v>4587</v>
+        <v>4450</v>
       </c>
       <c r="AM5" s="15" t="inlineStr">
         <is>
@@ -17171,21 +17171,21 @@
         </is>
       </c>
       <c r="AH6" s="15" t="n">
-        <v>21845</v>
+        <v>21929</v>
       </c>
       <c r="AI6" s="15" t="inlineStr">
         <is>
-          <t>https://www.sunadatosou.com/?p=21845</t>
+          <t>https://www.sunadatosou.com/?p=21929</t>
         </is>
       </c>
       <c r="AJ6" s="69" t="inlineStr">
         <is>
-          <t>2026-06-27 16:21:37</t>
+          <t>2026-06-27 16:59:54</t>
         </is>
       </c>
       <c r="AK6" s="69" t="str"/>
       <c r="AL6" s="15" t="n">
-        <v>4551</v>
+        <v>4414</v>
       </c>
       <c r="AM6" s="15" t="inlineStr">
         <is>

--- a/data/seo_80kw_production_management_v2_with_image_prompt_sheet.xlsx
+++ b/data/seo_80kw_production_management_v2_with_image_prompt_sheet.xlsx
@@ -17366,16 +17366,16 @@
         </is>
       </c>
       <c r="AH7" s="15" t="n">
-        <v>21849</v>
+        <v>21933</v>
       </c>
       <c r="AI7" s="15" t="inlineStr">
         <is>
-          <t>https://www.sunadatosou.com/?p=21849</t>
+          <t>https://www.sunadatosou.com/?p=21933</t>
         </is>
       </c>
       <c r="AJ7" s="69" t="inlineStr">
         <is>
-          <t>2026-06-27 16:26:49</t>
+          <t>2026-06-27 17:05:29</t>
         </is>
       </c>
       <c r="AK7" s="69" t="str"/>
@@ -17561,16 +17561,16 @@
         </is>
       </c>
       <c r="AH8" s="15" t="n">
-        <v>21851</v>
+        <v>21935</v>
       </c>
       <c r="AI8" s="15" t="inlineStr">
         <is>
-          <t>https://www.sunadatosou.com/?p=21851</t>
+          <t>https://www.sunadatosou.com/?p=21935</t>
         </is>
       </c>
       <c r="AJ8" s="69" t="inlineStr">
         <is>
-          <t>2026-06-27 16:26:58</t>
+          <t>2026-06-27 17:05:38</t>
         </is>
       </c>
       <c r="AK8" s="69" t="str"/>
@@ -17756,16 +17756,16 @@
         </is>
       </c>
       <c r="AH9" s="15" t="n">
-        <v>21853</v>
+        <v>21937</v>
       </c>
       <c r="AI9" s="15" t="inlineStr">
         <is>
-          <t>https://www.sunadatosou.com/?p=21853</t>
+          <t>https://www.sunadatosou.com/?p=21937</t>
         </is>
       </c>
       <c r="AJ9" s="69" t="inlineStr">
         <is>
-          <t>2026-06-27 16:27:08</t>
+          <t>2026-06-27 17:05:45</t>
         </is>
       </c>
       <c r="AK9" s="69" t="str"/>
@@ -17951,16 +17951,16 @@
         </is>
       </c>
       <c r="AH10" s="15" t="n">
-        <v>21855</v>
+        <v>21939</v>
       </c>
       <c r="AI10" s="15" t="inlineStr">
         <is>
-          <t>https://www.sunadatosou.com/?p=21855</t>
+          <t>https://www.sunadatosou.com/?p=21939</t>
         </is>
       </c>
       <c r="AJ10" s="69" t="inlineStr">
         <is>
-          <t>2026-06-27 16:27:16</t>
+          <t>2026-06-27 17:05:53</t>
         </is>
       </c>
       <c r="AK10" s="69" t="str"/>
@@ -18146,16 +18146,16 @@
         </is>
       </c>
       <c r="AH11" s="15" t="n">
-        <v>21857</v>
+        <v>21941</v>
       </c>
       <c r="AI11" s="15" t="inlineStr">
         <is>
-          <t>https://www.sunadatosou.com/?p=21857</t>
+          <t>https://www.sunadatosou.com/?p=21941</t>
         </is>
       </c>
       <c r="AJ11" s="69" t="inlineStr">
         <is>
-          <t>2026-06-27 16:27:24</t>
+          <t>2026-06-27 17:06:01</t>
         </is>
       </c>
       <c r="AK11" s="69" t="str"/>

--- a/data/seo_80kw_production_management_v2_with_image_prompt_sheet.xlsx
+++ b/data/seo_80kw_production_management_v2_with_image_prompt_sheet.xlsx
@@ -18322,7 +18322,7 @@
       </c>
       <c r="AD12" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE12" s="15" t="inlineStr">
@@ -18332,24 +18332,37 @@
       </c>
       <c r="AF12" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG12" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH12" s="15" t="str"/>
-      <c r="AI12" s="15" t="str"/>
-      <c r="AJ12" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH12" s="15" t="n">
+        <v>21943</v>
+      </c>
+      <c r="AI12" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21943</t>
+        </is>
+      </c>
+      <c r="AJ12" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:09:57</t>
+        </is>
+      </c>
       <c r="AK12" s="69" t="str"/>
-      <c r="AL12" s="15" t="str"/>
-      <c r="AM12" s="15">
-        <f>IF(AL12="","",IF(AL12&lt;I12,"不足",IF(AL12&gt;J12,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN12" s="15" t="str"/>
+      <c r="AL12" s="15" t="n">
+        <v>4306</v>
+      </c>
+      <c r="AM12" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN12" s="15" t="inlineStr"/>
       <c r="AO12" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の屋根修理」へリンク。関連：屋根カバー・屋根材注意記事。</t>
@@ -18504,7 +18517,7 @@
       </c>
       <c r="AD13" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE13" s="15" t="inlineStr">
@@ -18514,24 +18527,37 @@
       </c>
       <c r="AF13" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG13" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH13" s="15" t="str"/>
-      <c r="AI13" s="15" t="str"/>
-      <c r="AJ13" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH13" s="15" t="n">
+        <v>21945</v>
+      </c>
+      <c r="AI13" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21945</t>
+        </is>
+      </c>
+      <c r="AJ13" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:10:08</t>
+        </is>
+      </c>
       <c r="AK13" s="69" t="str"/>
-      <c r="AL13" s="15" t="str"/>
-      <c r="AM13" s="15">
-        <f>IF(AL13="","",IF(AL13&lt;I13,"不足",IF(AL13&gt;J13,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN13" s="15" t="str"/>
+      <c r="AL13" s="15" t="n">
+        <v>4302</v>
+      </c>
+      <c r="AM13" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN13" s="15" t="inlineStr"/>
       <c r="AO13" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の屋根修理」へリンク。関連：屋根カバー・屋根材注意記事。</t>
@@ -18686,7 +18712,7 @@
       </c>
       <c r="AD14" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE14" s="15" t="inlineStr">
@@ -18696,24 +18722,37 @@
       </c>
       <c r="AF14" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG14" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH14" s="15" t="str"/>
-      <c r="AI14" s="15" t="str"/>
-      <c r="AJ14" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH14" s="15" t="n">
+        <v>21947</v>
+      </c>
+      <c r="AI14" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21947</t>
+        </is>
+      </c>
+      <c r="AJ14" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:10:16</t>
+        </is>
+      </c>
       <c r="AK14" s="69" t="str"/>
-      <c r="AL14" s="15" t="str"/>
-      <c r="AM14" s="15">
-        <f>IF(AL14="","",IF(AL14&lt;I14,"不足",IF(AL14&gt;J14,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN14" s="15" t="str"/>
+      <c r="AL14" s="15" t="n">
+        <v>4340</v>
+      </c>
+      <c r="AM14" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN14" s="15" t="inlineStr"/>
       <c r="AO14" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の屋根修理」へリンク。関連：屋根カバー・屋根材注意記事。</t>
@@ -18868,7 +18907,7 @@
       </c>
       <c r="AD15" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE15" s="15" t="inlineStr">
@@ -18878,24 +18917,37 @@
       </c>
       <c r="AF15" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG15" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH15" s="15" t="str"/>
-      <c r="AI15" s="15" t="str"/>
-      <c r="AJ15" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH15" s="15" t="n">
+        <v>21949</v>
+      </c>
+      <c r="AI15" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21949</t>
+        </is>
+      </c>
+      <c r="AJ15" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:10:24</t>
+        </is>
+      </c>
       <c r="AK15" s="69" t="str"/>
-      <c r="AL15" s="15" t="str"/>
-      <c r="AM15" s="15">
-        <f>IF(AL15="","",IF(AL15&lt;I15,"不足",IF(AL15&gt;J15,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN15" s="15" t="str"/>
+      <c r="AL15" s="15" t="n">
+        <v>4318</v>
+      </c>
+      <c r="AM15" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN15" s="15" t="inlineStr"/>
       <c r="AO15" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の屋根修理」へリンク。関連：屋根カバー・屋根材注意記事。</t>
@@ -19050,7 +19102,7 @@
       </c>
       <c r="AD16" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE16" s="15" t="inlineStr">
@@ -19060,24 +19112,37 @@
       </c>
       <c r="AF16" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG16" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH16" s="15" t="str"/>
-      <c r="AI16" s="15" t="str"/>
-      <c r="AJ16" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH16" s="15" t="n">
+        <v>21951</v>
+      </c>
+      <c r="AI16" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21951</t>
+        </is>
+      </c>
+      <c r="AJ16" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:10:31</t>
+        </is>
+      </c>
       <c r="AK16" s="69" t="str"/>
-      <c r="AL16" s="15" t="str"/>
-      <c r="AM16" s="15">
-        <f>IF(AL16="","",IF(AL16&lt;I16,"不足",IF(AL16&gt;J16,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN16" s="15" t="str"/>
+      <c r="AL16" s="15" t="n">
+        <v>4289</v>
+      </c>
+      <c r="AM16" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN16" s="15" t="inlineStr"/>
       <c r="AO16" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の屋根修理」へリンク。関連：屋根カバー・屋根材注意記事。</t>
@@ -19232,7 +19297,7 @@
       </c>
       <c r="AD17" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE17" s="15" t="inlineStr">
@@ -19242,24 +19307,37 @@
       </c>
       <c r="AF17" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG17" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH17" s="15" t="str"/>
-      <c r="AI17" s="15" t="str"/>
-      <c r="AJ17" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH17" s="15" t="n">
+        <v>21953</v>
+      </c>
+      <c r="AI17" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21953</t>
+        </is>
+      </c>
+      <c r="AJ17" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:10:40</t>
+        </is>
+      </c>
       <c r="AK17" s="69" t="str"/>
-      <c r="AL17" s="15" t="str"/>
-      <c r="AM17" s="15">
-        <f>IF(AL17="","",IF(AL17&lt;I17,"不足",IF(AL17&gt;J17,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN17" s="15" t="str"/>
+      <c r="AL17" s="15" t="n">
+        <v>4369</v>
+      </c>
+      <c r="AM17" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN17" s="15" t="inlineStr"/>
       <c r="AO17" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の屋根修理」へリンク。関連：屋根カバー・屋根材注意記事。</t>
@@ -19414,7 +19492,7 @@
       </c>
       <c r="AD18" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE18" s="15" t="inlineStr">
@@ -19424,24 +19502,37 @@
       </c>
       <c r="AF18" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG18" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH18" s="15" t="str"/>
-      <c r="AI18" s="15" t="str"/>
-      <c r="AJ18" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH18" s="15" t="n">
+        <v>21955</v>
+      </c>
+      <c r="AI18" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21955</t>
+        </is>
+      </c>
+      <c r="AJ18" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:10:50</t>
+        </is>
+      </c>
       <c r="AK18" s="69" t="str"/>
-      <c r="AL18" s="15" t="str"/>
-      <c r="AM18" s="15">
-        <f>IF(AL18="","",IF(AL18&lt;I18,"不足",IF(AL18&gt;J18,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN18" s="15" t="str"/>
+      <c r="AL18" s="15" t="n">
+        <v>4311</v>
+      </c>
+      <c r="AM18" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN18" s="15" t="inlineStr"/>
       <c r="AO18" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の屋根修理」へリンク。関連：屋根カバー・屋根材注意記事。</t>
@@ -19596,7 +19687,7 @@
       </c>
       <c r="AD19" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE19" s="15" t="inlineStr">
@@ -19606,24 +19697,37 @@
       </c>
       <c r="AF19" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG19" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH19" s="15" t="str"/>
-      <c r="AI19" s="15" t="str"/>
-      <c r="AJ19" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH19" s="15" t="n">
+        <v>21957</v>
+      </c>
+      <c r="AI19" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21957</t>
+        </is>
+      </c>
+      <c r="AJ19" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:10:58</t>
+        </is>
+      </c>
       <c r="AK19" s="69" t="str"/>
-      <c r="AL19" s="15" t="str"/>
-      <c r="AM19" s="15">
-        <f>IF(AL19="","",IF(AL19&lt;I19,"不足",IF(AL19&gt;J19,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN19" s="15" t="str"/>
+      <c r="AL19" s="15" t="n">
+        <v>4240</v>
+      </c>
+      <c r="AM19" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN19" s="15" t="inlineStr"/>
       <c r="AO19" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の屋根修理」へリンク。関連：屋根カバー・屋根材注意記事。</t>
@@ -19778,7 +19882,7 @@
       </c>
       <c r="AD20" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE20" s="15" t="inlineStr">
@@ -19788,24 +19892,37 @@
       </c>
       <c r="AF20" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG20" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH20" s="15" t="str"/>
-      <c r="AI20" s="15" t="str"/>
-      <c r="AJ20" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH20" s="15" t="n">
+        <v>21959</v>
+      </c>
+      <c r="AI20" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21959</t>
+        </is>
+      </c>
+      <c r="AJ20" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:11:09</t>
+        </is>
+      </c>
       <c r="AK20" s="69" t="str"/>
-      <c r="AL20" s="15" t="str"/>
-      <c r="AM20" s="15">
-        <f>IF(AL20="","",IF(AL20&lt;I20,"不足",IF(AL20&gt;J20,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN20" s="15" t="str"/>
+      <c r="AL20" s="15" t="n">
+        <v>4275</v>
+      </c>
+      <c r="AM20" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN20" s="15" t="inlineStr"/>
       <c r="AO20" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の屋根修理」へリンク。関連：屋根カバー・屋根材注意記事。</t>
@@ -19960,7 +20077,7 @@
       </c>
       <c r="AD21" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE21" s="15" t="inlineStr">
@@ -19970,24 +20087,37 @@
       </c>
       <c r="AF21" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG21" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH21" s="15" t="str"/>
-      <c r="AI21" s="15" t="str"/>
-      <c r="AJ21" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH21" s="15" t="n">
+        <v>21961</v>
+      </c>
+      <c r="AI21" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21961</t>
+        </is>
+      </c>
+      <c r="AJ21" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:11:18</t>
+        </is>
+      </c>
       <c r="AK21" s="69" t="str"/>
-      <c r="AL21" s="15" t="str"/>
-      <c r="AM21" s="15">
-        <f>IF(AL21="","",IF(AL21&lt;I21,"不足",IF(AL21&gt;J21,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN21" s="15" t="str"/>
+      <c r="AL21" s="15" t="n">
+        <v>3315</v>
+      </c>
+      <c r="AM21" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN21" s="15" t="inlineStr"/>
       <c r="AO21" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装工期、足場代、防水工事、屋根カバーへリンク。</t>
@@ -20142,7 +20272,7 @@
       </c>
       <c r="AD22" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE22" s="15" t="inlineStr">
@@ -20152,24 +20282,37 @@
       </c>
       <c r="AF22" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG22" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH22" s="15" t="str"/>
-      <c r="AI22" s="15" t="str"/>
-      <c r="AJ22" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH22" s="15" t="n">
+        <v>21963</v>
+      </c>
+      <c r="AI22" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21963</t>
+        </is>
+      </c>
+      <c r="AJ22" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:11:25</t>
+        </is>
+      </c>
       <c r="AK22" s="69" t="str"/>
-      <c r="AL22" s="15" t="str"/>
-      <c r="AM22" s="15">
-        <f>IF(AL22="","",IF(AL22&lt;I22,"不足",IF(AL22&gt;J22,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN22" s="15" t="str"/>
+      <c r="AL22" s="15" t="n">
+        <v>3256</v>
+      </c>
+      <c r="AM22" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN22" s="15" t="inlineStr"/>
       <c r="AO22" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装工期、足場代、防水工事、屋根カバーへリンク。</t>
@@ -20324,7 +20467,7 @@
       </c>
       <c r="AD23" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE23" s="15" t="inlineStr">
@@ -20334,24 +20477,37 @@
       </c>
       <c r="AF23" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG23" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH23" s="15" t="str"/>
-      <c r="AI23" s="15" t="str"/>
-      <c r="AJ23" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH23" s="15" t="n">
+        <v>21965</v>
+      </c>
+      <c r="AI23" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21965</t>
+        </is>
+      </c>
+      <c r="AJ23" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:11:33</t>
+        </is>
+      </c>
       <c r="AK23" s="69" t="str"/>
-      <c r="AL23" s="15" t="str"/>
-      <c r="AM23" s="15">
-        <f>IF(AL23="","",IF(AL23&lt;I23,"不足",IF(AL23&gt;J23,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN23" s="15" t="str"/>
+      <c r="AL23" s="15" t="n">
+        <v>3284</v>
+      </c>
+      <c r="AM23" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN23" s="15" t="inlineStr"/>
       <c r="AO23" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装工期、足場代、防水工事、屋根カバーへリンク。</t>
@@ -20506,7 +20662,7 @@
       </c>
       <c r="AD24" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE24" s="15" t="inlineStr">
@@ -20516,24 +20672,37 @@
       </c>
       <c r="AF24" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG24" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH24" s="15" t="str"/>
-      <c r="AI24" s="15" t="str"/>
-      <c r="AJ24" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH24" s="15" t="n">
+        <v>21967</v>
+      </c>
+      <c r="AI24" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21967</t>
+        </is>
+      </c>
+      <c r="AJ24" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:11:41</t>
+        </is>
+      </c>
       <c r="AK24" s="69" t="str"/>
-      <c r="AL24" s="15" t="str"/>
-      <c r="AM24" s="15">
-        <f>IF(AL24="","",IF(AL24&lt;I24,"不足",IF(AL24&gt;J24,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN24" s="15" t="str"/>
+      <c r="AL24" s="15" t="n">
+        <v>3276</v>
+      </c>
+      <c r="AM24" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN24" s="15" t="inlineStr"/>
       <c r="AO24" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装工期、足場代、防水工事、屋根カバーへリンク。</t>
@@ -20688,7 +20857,7 @@
       </c>
       <c r="AD25" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE25" s="15" t="inlineStr">
@@ -20698,24 +20867,37 @@
       </c>
       <c r="AF25" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG25" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH25" s="15" t="str"/>
-      <c r="AI25" s="15" t="str"/>
-      <c r="AJ25" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH25" s="15" t="n">
+        <v>21969</v>
+      </c>
+      <c r="AI25" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21969</t>
+        </is>
+      </c>
+      <c r="AJ25" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:11:49</t>
+        </is>
+      </c>
       <c r="AK25" s="69" t="str"/>
-      <c r="AL25" s="15" t="str"/>
-      <c r="AM25" s="15">
-        <f>IF(AL25="","",IF(AL25&lt;I25,"不足",IF(AL25&gt;J25,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN25" s="15" t="str"/>
+      <c r="AL25" s="15" t="n">
+        <v>3267</v>
+      </c>
+      <c r="AM25" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN25" s="15" t="inlineStr"/>
       <c r="AO25" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装工期、足場代、防水工事、屋根カバーへリンク。</t>
@@ -20870,7 +21052,7 @@
       </c>
       <c r="AD26" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE26" s="15" t="inlineStr">
@@ -20880,24 +21062,37 @@
       </c>
       <c r="AF26" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG26" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH26" s="15" t="str"/>
-      <c r="AI26" s="15" t="str"/>
-      <c r="AJ26" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH26" s="15" t="n">
+        <v>21971</v>
+      </c>
+      <c r="AI26" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21971</t>
+        </is>
+      </c>
+      <c r="AJ26" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:11:58</t>
+        </is>
+      </c>
       <c r="AK26" s="69" t="str"/>
-      <c r="AL26" s="15" t="str"/>
-      <c r="AM26" s="15">
-        <f>IF(AL26="","",IF(AL26&lt;I26,"不足",IF(AL26&gt;J26,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN26" s="15" t="str"/>
+      <c r="AL26" s="15" t="n">
+        <v>3186</v>
+      </c>
+      <c r="AM26" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,500字)</t>
+        </is>
+      </c>
+      <c r="AN26" s="15" t="inlineStr"/>
       <c r="AO26" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の雨漏り修理」へリンク。関連：雨漏り費用・調査・屋根雨漏り。</t>
@@ -21052,7 +21247,7 @@
       </c>
       <c r="AD27" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE27" s="15" t="inlineStr">
@@ -21062,24 +21257,37 @@
       </c>
       <c r="AF27" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG27" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH27" s="15" t="str"/>
-      <c r="AI27" s="15" t="str"/>
-      <c r="AJ27" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH27" s="15" t="n">
+        <v>21973</v>
+      </c>
+      <c r="AI27" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21973</t>
+        </is>
+      </c>
+      <c r="AJ27" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:12:06</t>
+        </is>
+      </c>
       <c r="AK27" s="69" t="str"/>
-      <c r="AL27" s="15" t="str"/>
-      <c r="AM27" s="15">
-        <f>IF(AL27="","",IF(AL27&lt;I27,"不足",IF(AL27&gt;J27,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN27" s="15" t="str"/>
+      <c r="AL27" s="15" t="n">
+        <v>3177</v>
+      </c>
+      <c r="AM27" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,500字)</t>
+        </is>
+      </c>
+      <c r="AN27" s="15" t="inlineStr"/>
       <c r="AO27" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の雨漏り修理」へリンク。関連：雨漏り費用・調査・屋根雨漏り。</t>
@@ -21234,7 +21442,7 @@
       </c>
       <c r="AD28" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE28" s="15" t="inlineStr">
@@ -21244,24 +21452,37 @@
       </c>
       <c r="AF28" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG28" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH28" s="15" t="str"/>
-      <c r="AI28" s="15" t="str"/>
-      <c r="AJ28" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH28" s="15" t="n">
+        <v>21975</v>
+      </c>
+      <c r="AI28" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21975</t>
+        </is>
+      </c>
+      <c r="AJ28" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:12:13</t>
+        </is>
+      </c>
       <c r="AK28" s="69" t="str"/>
-      <c r="AL28" s="15" t="str"/>
-      <c r="AM28" s="15">
-        <f>IF(AL28="","",IF(AL28&lt;I28,"不足",IF(AL28&gt;J28,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN28" s="15" t="str"/>
+      <c r="AL28" s="15" t="n">
+        <v>3121</v>
+      </c>
+      <c r="AM28" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,500字)</t>
+        </is>
+      </c>
+      <c r="AN28" s="15" t="inlineStr"/>
       <c r="AO28" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の雨漏り修理」へリンク。関連：雨漏り費用・調査・屋根雨漏り。</t>
@@ -21416,7 +21637,7 @@
       </c>
       <c r="AD29" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE29" s="15" t="inlineStr">
@@ -21426,24 +21647,37 @@
       </c>
       <c r="AF29" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG29" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH29" s="15" t="str"/>
-      <c r="AI29" s="15" t="str"/>
-      <c r="AJ29" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH29" s="15" t="n">
+        <v>21977</v>
+      </c>
+      <c r="AI29" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21977</t>
+        </is>
+      </c>
+      <c r="AJ29" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:12:21</t>
+        </is>
+      </c>
       <c r="AK29" s="69" t="str"/>
-      <c r="AL29" s="15" t="str"/>
-      <c r="AM29" s="15">
-        <f>IF(AL29="","",IF(AL29&lt;I29,"不足",IF(AL29&gt;J29,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN29" s="15" t="str"/>
+      <c r="AL29" s="15" t="n">
+        <v>3125</v>
+      </c>
+      <c r="AM29" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,500字)</t>
+        </is>
+      </c>
+      <c r="AN29" s="15" t="inlineStr"/>
       <c r="AO29" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の雨漏り修理」へリンク。関連：雨漏り費用・調査・屋根雨漏り。</t>
@@ -21598,7 +21832,7 @@
       </c>
       <c r="AD30" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE30" s="15" t="inlineStr">
@@ -21608,24 +21842,37 @@
       </c>
       <c r="AF30" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG30" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH30" s="15" t="str"/>
-      <c r="AI30" s="15" t="str"/>
-      <c r="AJ30" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH30" s="15" t="n">
+        <v>21979</v>
+      </c>
+      <c r="AI30" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21979</t>
+        </is>
+      </c>
+      <c r="AJ30" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:12:29</t>
+        </is>
+      </c>
       <c r="AK30" s="69" t="str"/>
-      <c r="AL30" s="15" t="str"/>
-      <c r="AM30" s="15">
-        <f>IF(AL30="","",IF(AL30&lt;I30,"不足",IF(AL30&gt;J30,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN30" s="15" t="str"/>
+      <c r="AL30" s="15" t="n">
+        <v>3135</v>
+      </c>
+      <c r="AM30" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,500字)</t>
+        </is>
+      </c>
+      <c r="AN30" s="15" t="inlineStr"/>
       <c r="AO30" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の雨漏り修理」へリンク。関連：雨漏り費用・調査・屋根雨漏り。</t>
@@ -21780,7 +22027,7 @@
       </c>
       <c r="AD31" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE31" s="15" t="inlineStr">
@@ -21790,24 +22037,37 @@
       </c>
       <c r="AF31" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG31" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH31" s="15" t="str"/>
-      <c r="AI31" s="15" t="str"/>
-      <c r="AJ31" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH31" s="15" t="n">
+        <v>21981</v>
+      </c>
+      <c r="AI31" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21981</t>
+        </is>
+      </c>
+      <c r="AJ31" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:12:37</t>
+        </is>
+      </c>
       <c r="AK31" s="69" t="str"/>
-      <c r="AL31" s="15" t="str"/>
-      <c r="AM31" s="15">
-        <f>IF(AL31="","",IF(AL31&lt;I31,"不足",IF(AL31&gt;J31,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN31" s="15" t="str"/>
+      <c r="AL31" s="15" t="n">
+        <v>3161</v>
+      </c>
+      <c r="AM31" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,500字)</t>
+        </is>
+      </c>
+      <c r="AN31" s="15" t="inlineStr"/>
       <c r="AO31" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の雨漏り修理」へリンク。関連：雨漏り費用・調査・屋根雨漏り。</t>
@@ -21962,7 +22222,7 @@
       </c>
       <c r="AD32" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE32" s="15" t="inlineStr">
@@ -21972,24 +22232,37 @@
       </c>
       <c r="AF32" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG32" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH32" s="15" t="str"/>
-      <c r="AI32" s="15" t="str"/>
-      <c r="AJ32" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH32" s="15" t="n">
+        <v>21983</v>
+      </c>
+      <c r="AI32" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21983</t>
+        </is>
+      </c>
+      <c r="AJ32" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:12:46</t>
+        </is>
+      </c>
       <c r="AK32" s="69" t="str"/>
-      <c r="AL32" s="15" t="str"/>
-      <c r="AM32" s="15">
-        <f>IF(AL32="","",IF(AL32&lt;I32,"不足",IF(AL32&gt;J32,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN32" s="15" t="str"/>
+      <c r="AL32" s="15" t="n">
+        <v>3834</v>
+      </c>
+      <c r="AM32" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,500字)</t>
+        </is>
+      </c>
+      <c r="AN32" s="15" t="inlineStr"/>
       <c r="AO32" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の雨漏り修理」へリンク。関連：雨漏り費用・調査・屋根雨漏り。</t>
@@ -22144,7 +22417,7 @@
       </c>
       <c r="AD33" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE33" s="15" t="inlineStr">
@@ -22154,24 +22427,37 @@
       </c>
       <c r="AF33" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG33" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH33" s="15" t="str"/>
-      <c r="AI33" s="15" t="str"/>
-      <c r="AJ33" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH33" s="15" t="n">
+        <v>21985</v>
+      </c>
+      <c r="AI33" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21985</t>
+        </is>
+      </c>
+      <c r="AJ33" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:12:57</t>
+        </is>
+      </c>
       <c r="AK33" s="69" t="str"/>
-      <c r="AL33" s="15" t="str"/>
-      <c r="AM33" s="15">
-        <f>IF(AL33="","",IF(AL33&lt;I33,"不足",IF(AL33&gt;J33,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN33" s="15" t="str"/>
+      <c r="AL33" s="15" t="n">
+        <v>4285</v>
+      </c>
+      <c r="AM33" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN33" s="15" t="inlineStr"/>
       <c r="AO33" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の雨漏り修理」へリンク。関連：雨漏り費用・調査・屋根雨漏り。</t>
@@ -22326,7 +22612,7 @@
       </c>
       <c r="AD34" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE34" s="15" t="inlineStr">
@@ -22336,24 +22622,37 @@
       </c>
       <c r="AF34" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG34" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH34" s="15" t="str"/>
-      <c r="AI34" s="15" t="str"/>
-      <c r="AJ34" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH34" s="15" t="n">
+        <v>21987</v>
+      </c>
+      <c r="AI34" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21987</t>
+        </is>
+      </c>
+      <c r="AJ34" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:13:05</t>
+        </is>
+      </c>
       <c r="AK34" s="69" t="str"/>
-      <c r="AL34" s="15" t="str"/>
-      <c r="AM34" s="15">
-        <f>IF(AL34="","",IF(AL34&lt;I34,"不足",IF(AL34&gt;J34,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN34" s="15" t="str"/>
+      <c r="AL34" s="15" t="n">
+        <v>3842</v>
+      </c>
+      <c r="AM34" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN34" s="15" t="inlineStr"/>
       <c r="AO34" s="15" t="inlineStr">
         <is>
           <t>関連：ベランダ防水費用、シーリング打ち替え費用、外壁雨漏りへリンク。</t>
@@ -22508,7 +22807,7 @@
       </c>
       <c r="AD35" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE35" s="15" t="inlineStr">
@@ -22518,24 +22817,37 @@
       </c>
       <c r="AF35" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG35" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH35" s="15" t="str"/>
-      <c r="AI35" s="15" t="str"/>
-      <c r="AJ35" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH35" s="15" t="n">
+        <v>21989</v>
+      </c>
+      <c r="AI35" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21989</t>
+        </is>
+      </c>
+      <c r="AJ35" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:13:13</t>
+        </is>
+      </c>
       <c r="AK35" s="69" t="str"/>
-      <c r="AL35" s="15" t="str"/>
-      <c r="AM35" s="15">
-        <f>IF(AL35="","",IF(AL35&lt;I35,"不足",IF(AL35&gt;J35,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN35" s="15" t="str"/>
+      <c r="AL35" s="15" t="n">
+        <v>3840</v>
+      </c>
+      <c r="AM35" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN35" s="15" t="inlineStr"/>
       <c r="AO35" s="15" t="inlineStr">
         <is>
           <t>関連：ベランダ防水費用、シーリング打ち替え費用、外壁雨漏りへリンク。</t>
@@ -22690,7 +23002,7 @@
       </c>
       <c r="AD36" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE36" s="15" t="inlineStr">
@@ -22700,24 +23012,37 @@
       </c>
       <c r="AF36" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG36" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH36" s="15" t="str"/>
-      <c r="AI36" s="15" t="str"/>
-      <c r="AJ36" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH36" s="15" t="n">
+        <v>21991</v>
+      </c>
+      <c r="AI36" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21991</t>
+        </is>
+      </c>
+      <c r="AJ36" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:13:25</t>
+        </is>
+      </c>
       <c r="AK36" s="69" t="str"/>
-      <c r="AL36" s="15" t="str"/>
-      <c r="AM36" s="15">
-        <f>IF(AL36="","",IF(AL36&lt;I36,"不足",IF(AL36&gt;J36,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN36" s="15" t="str"/>
+      <c r="AL36" s="15" t="n">
+        <v>4185</v>
+      </c>
+      <c r="AM36" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN36" s="15" t="inlineStr"/>
       <c r="AO36" s="15" t="inlineStr">
         <is>
           <t>関連：ベランダ防水費用、シーリング打ち替え費用、外壁雨漏りへリンク。</t>
@@ -22872,7 +23197,7 @@
       </c>
       <c r="AD37" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE37" s="15" t="inlineStr">
@@ -22882,24 +23207,37 @@
       </c>
       <c r="AF37" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG37" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH37" s="15" t="str"/>
-      <c r="AI37" s="15" t="str"/>
-      <c r="AJ37" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH37" s="15" t="n">
+        <v>21993</v>
+      </c>
+      <c r="AI37" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21993</t>
+        </is>
+      </c>
+      <c r="AJ37" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:13:33</t>
+        </is>
+      </c>
       <c r="AK37" s="69" t="str"/>
-      <c r="AL37" s="15" t="str"/>
-      <c r="AM37" s="15">
-        <f>IF(AL37="","",IF(AL37&lt;I37,"不足",IF(AL37&gt;J37,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN37" s="15" t="str"/>
+      <c r="AL37" s="15" t="n">
+        <v>4183</v>
+      </c>
+      <c r="AM37" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN37" s="15" t="inlineStr"/>
       <c r="AO37" s="15" t="inlineStr">
         <is>
           <t>関連：ベランダ防水費用、シーリング打ち替え費用、外壁雨漏りへリンク。</t>
@@ -23054,7 +23392,7 @@
       </c>
       <c r="AD38" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE38" s="15" t="inlineStr">
@@ -23064,24 +23402,37 @@
       </c>
       <c r="AF38" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG38" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH38" s="15" t="str"/>
-      <c r="AI38" s="15" t="str"/>
-      <c r="AJ38" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH38" s="15" t="n">
+        <v>21995</v>
+      </c>
+      <c r="AI38" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21995</t>
+        </is>
+      </c>
+      <c r="AJ38" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:13:43</t>
+        </is>
+      </c>
       <c r="AK38" s="69" t="str"/>
-      <c r="AL38" s="15" t="str"/>
-      <c r="AM38" s="15">
-        <f>IF(AL38="","",IF(AL38&lt;I38,"不足",IF(AL38&gt;J38,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN38" s="15" t="str"/>
+      <c r="AL38" s="15" t="n">
+        <v>4201</v>
+      </c>
+      <c r="AM38" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN38" s="15" t="inlineStr"/>
       <c r="AO38" s="15" t="inlineStr">
         <is>
           <t>関連：ベランダ防水費用、シーリング打ち替え費用、外壁雨漏りへリンク。</t>
@@ -23236,7 +23587,7 @@
       </c>
       <c r="AD39" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE39" s="15" t="inlineStr">
@@ -23246,24 +23597,37 @@
       </c>
       <c r="AF39" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG39" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH39" s="15" t="str"/>
-      <c r="AI39" s="15" t="str"/>
-      <c r="AJ39" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH39" s="15" t="n">
+        <v>21997</v>
+      </c>
+      <c r="AI39" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21997</t>
+        </is>
+      </c>
+      <c r="AJ39" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:13:51</t>
+        </is>
+      </c>
       <c r="AK39" s="69" t="str"/>
-      <c r="AL39" s="15" t="str"/>
-      <c r="AM39" s="15">
-        <f>IF(AL39="","",IF(AL39&lt;I39,"不足",IF(AL39&gt;J39,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN39" s="15" t="str"/>
+      <c r="AL39" s="15" t="n">
+        <v>3792</v>
+      </c>
+      <c r="AM39" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN39" s="15" t="inlineStr"/>
       <c r="AO39" s="15" t="inlineStr">
         <is>
           <t>関連：ベランダ防水費用、シーリング打ち替え費用、外壁雨漏りへリンク。</t>
@@ -23418,7 +23782,7 @@
       </c>
       <c r="AD40" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE40" s="15" t="inlineStr">
@@ -23428,24 +23792,37 @@
       </c>
       <c r="AF40" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG40" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH40" s="15" t="str"/>
-      <c r="AI40" s="15" t="str"/>
-      <c r="AJ40" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH40" s="15" t="n">
+        <v>21999</v>
+      </c>
+      <c r="AI40" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21999</t>
+        </is>
+      </c>
+      <c r="AJ40" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:14:01</t>
+        </is>
+      </c>
       <c r="AK40" s="69" t="str"/>
-      <c r="AL40" s="15" t="str"/>
-      <c r="AM40" s="15">
-        <f>IF(AL40="","",IF(AL40&lt;I40,"不足",IF(AL40&gt;J40,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN40" s="15" t="str"/>
+      <c r="AL40" s="15" t="n">
+        <v>3801</v>
+      </c>
+      <c r="AM40" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN40" s="15" t="inlineStr"/>
       <c r="AO40" s="15" t="inlineStr">
         <is>
           <t>関連：ベランダ防水費用、シーリング打ち替え費用、外壁雨漏りへリンク。</t>
@@ -23600,7 +23977,7 @@
       </c>
       <c r="AD41" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE41" s="15" t="inlineStr">
@@ -23610,24 +23987,37 @@
       </c>
       <c r="AF41" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG41" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH41" s="15" t="str"/>
-      <c r="AI41" s="15" t="str"/>
-      <c r="AJ41" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH41" s="15" t="n">
+        <v>22001</v>
+      </c>
+      <c r="AI41" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22001</t>
+        </is>
+      </c>
+      <c r="AJ41" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:14:12</t>
+        </is>
+      </c>
       <c r="AK41" s="69" t="str"/>
-      <c r="AL41" s="15" t="str"/>
-      <c r="AM41" s="15">
-        <f>IF(AL41="","",IF(AL41&lt;I41,"不足",IF(AL41&gt;J41,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN41" s="15" t="str"/>
+      <c r="AL41" s="15" t="n">
+        <v>3800</v>
+      </c>
+      <c r="AM41" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN41" s="15" t="inlineStr"/>
       <c r="AO41" s="15" t="inlineStr">
         <is>
           <t>関連：ベランダ防水費用、シーリング打ち替え費用、外壁雨漏りへリンク。</t>
@@ -23782,7 +24172,7 @@
       </c>
       <c r="AD42" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE42" s="15" t="inlineStr">
@@ -23792,24 +24182,37 @@
       </c>
       <c r="AF42" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG42" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH42" s="15" t="str"/>
-      <c r="AI42" s="15" t="str"/>
-      <c r="AJ42" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH42" s="15" t="n">
+        <v>22003</v>
+      </c>
+      <c r="AI42" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22003</t>
+        </is>
+      </c>
+      <c r="AJ42" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:14:22</t>
+        </is>
+      </c>
       <c r="AK42" s="69" t="str"/>
-      <c r="AL42" s="15" t="str"/>
-      <c r="AM42" s="15">
-        <f>IF(AL42="","",IF(AL42&lt;I42,"不足",IF(AL42&gt;J42,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN42" s="15" t="str"/>
+      <c r="AL42" s="15" t="n">
+        <v>4155</v>
+      </c>
+      <c r="AM42" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN42" s="15" t="inlineStr"/>
       <c r="AO42" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の屋根修理」へリンク。関連：屋根カバー・屋根材注意記事。</t>
@@ -24146,7 +24549,7 @@
       </c>
       <c r="AD44" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE44" s="15" t="inlineStr">
@@ -24156,24 +24559,37 @@
       </c>
       <c r="AF44" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG44" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH44" s="15" t="str"/>
-      <c r="AI44" s="15" t="str"/>
-      <c r="AJ44" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH44" s="15" t="n">
+        <v>22005</v>
+      </c>
+      <c r="AI44" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22005</t>
+        </is>
+      </c>
+      <c r="AJ44" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:14:31</t>
+        </is>
+      </c>
       <c r="AK44" s="69" t="str"/>
-      <c r="AL44" s="15" t="str"/>
-      <c r="AM44" s="15">
-        <f>IF(AL44="","",IF(AL44&lt;I44,"不足",IF(AL44&gt;J44,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN44" s="15" t="str"/>
+      <c r="AL44" s="15" t="n">
+        <v>4169</v>
+      </c>
+      <c r="AM44" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN44" s="15" t="inlineStr"/>
       <c r="AO44" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の屋根修理」へリンク。関連：屋根カバー・屋根材注意記事。</t>
@@ -24328,7 +24744,7 @@
       </c>
       <c r="AD45" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE45" s="15" t="inlineStr">
@@ -24338,24 +24754,37 @@
       </c>
       <c r="AF45" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG45" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH45" s="15" t="str"/>
-      <c r="AI45" s="15" t="str"/>
-      <c r="AJ45" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH45" s="15" t="n">
+        <v>22007</v>
+      </c>
+      <c r="AI45" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22007</t>
+        </is>
+      </c>
+      <c r="AJ45" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:14:39</t>
+        </is>
+      </c>
       <c r="AK45" s="69" t="str"/>
-      <c r="AL45" s="15" t="str"/>
-      <c r="AM45" s="15">
-        <f>IF(AL45="","",IF(AL45&lt;I45,"不足",IF(AL45&gt;J45,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN45" s="15" t="str"/>
+      <c r="AL45" s="15" t="n">
+        <v>4148</v>
+      </c>
+      <c r="AM45" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN45" s="15" t="inlineStr"/>
       <c r="AO45" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の屋根修理」へリンク。関連：屋根カバー・屋根材注意記事。</t>
@@ -24510,7 +24939,7 @@
       </c>
       <c r="AD46" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE46" s="15" t="inlineStr">
@@ -24520,24 +24949,37 @@
       </c>
       <c r="AF46" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG46" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH46" s="15" t="str"/>
-      <c r="AI46" s="15" t="str"/>
-      <c r="AJ46" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH46" s="15" t="n">
+        <v>22009</v>
+      </c>
+      <c r="AI46" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22009</t>
+        </is>
+      </c>
+      <c r="AJ46" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:14:47</t>
+        </is>
+      </c>
       <c r="AK46" s="69" t="str"/>
-      <c r="AL46" s="15" t="str"/>
-      <c r="AM46" s="15">
-        <f>IF(AL46="","",IF(AL46&lt;I46,"不足",IF(AL46&gt;J46,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN46" s="15" t="str"/>
+      <c r="AL46" s="15" t="n">
+        <v>4178</v>
+      </c>
+      <c r="AM46" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN46" s="15" t="inlineStr"/>
       <c r="AO46" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の屋根修理」へリンク。関連：屋根カバー・屋根材注意記事。</t>
@@ -24692,7 +25134,7 @@
       </c>
       <c r="AD47" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE47" s="15" t="inlineStr">
@@ -24702,24 +25144,37 @@
       </c>
       <c r="AF47" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG47" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH47" s="15" t="str"/>
-      <c r="AI47" s="15" t="str"/>
-      <c r="AJ47" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH47" s="15" t="n">
+        <v>22011</v>
+      </c>
+      <c r="AI47" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22011</t>
+        </is>
+      </c>
+      <c r="AJ47" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:14:55</t>
+        </is>
+      </c>
       <c r="AK47" s="69" t="str"/>
-      <c r="AL47" s="15" t="str"/>
-      <c r="AM47" s="15">
-        <f>IF(AL47="","",IF(AL47&lt;I47,"不足",IF(AL47&gt;J47,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN47" s="15" t="str"/>
+      <c r="AL47" s="15" t="n">
+        <v>4158</v>
+      </c>
+      <c r="AM47" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN47" s="15" t="inlineStr"/>
       <c r="AO47" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の屋根修理」へリンク。関連：屋根カバー・屋根材注意記事。</t>
@@ -24874,7 +25329,7 @@
       </c>
       <c r="AD48" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE48" s="15" t="inlineStr">
@@ -24884,24 +25339,37 @@
       </c>
       <c r="AF48" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG48" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH48" s="15" t="str"/>
-      <c r="AI48" s="15" t="str"/>
-      <c r="AJ48" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH48" s="15" t="n">
+        <v>22013</v>
+      </c>
+      <c r="AI48" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22013</t>
+        </is>
+      </c>
+      <c r="AJ48" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:15:06</t>
+        </is>
+      </c>
       <c r="AK48" s="69" t="str"/>
-      <c r="AL48" s="15" t="str"/>
-      <c r="AM48" s="15">
-        <f>IF(AL48="","",IF(AL48&lt;I48,"不足",IF(AL48&gt;J48,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN48" s="15" t="str"/>
+      <c r="AL48" s="15" t="n">
+        <v>4175</v>
+      </c>
+      <c r="AM48" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN48" s="15" t="inlineStr"/>
       <c r="AO48" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の屋根修理」へリンク。関連：屋根カバー・屋根材注意記事。</t>
@@ -25056,7 +25524,7 @@
       </c>
       <c r="AD49" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE49" s="15" t="inlineStr">
@@ -25066,24 +25534,37 @@
       </c>
       <c r="AF49" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG49" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH49" s="15" t="str"/>
-      <c r="AI49" s="15" t="str"/>
-      <c r="AJ49" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH49" s="15" t="n">
+        <v>22015</v>
+      </c>
+      <c r="AI49" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22015</t>
+        </is>
+      </c>
+      <c r="AJ49" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:15:18</t>
+        </is>
+      </c>
       <c r="AK49" s="69" t="str"/>
-      <c r="AL49" s="15" t="str"/>
-      <c r="AM49" s="15">
-        <f>IF(AL49="","",IF(AL49&lt;I49,"不足",IF(AL49&gt;J49,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN49" s="15" t="str"/>
+      <c r="AL49" s="15" t="n">
+        <v>4171</v>
+      </c>
+      <c r="AM49" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN49" s="15" t="inlineStr"/>
       <c r="AO49" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の屋根修理」へリンク。関連：屋根カバー・屋根材注意記事。</t>
@@ -25238,7 +25719,7 @@
       </c>
       <c r="AD50" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE50" s="15" t="inlineStr">
@@ -25248,24 +25729,37 @@
       </c>
       <c r="AF50" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG50" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH50" s="15" t="str"/>
-      <c r="AI50" s="15" t="str"/>
-      <c r="AJ50" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH50" s="15" t="n">
+        <v>22017</v>
+      </c>
+      <c r="AI50" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22017</t>
+        </is>
+      </c>
+      <c r="AJ50" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:15:29</t>
+        </is>
+      </c>
       <c r="AK50" s="69" t="str"/>
-      <c r="AL50" s="15" t="str"/>
-      <c r="AM50" s="15">
-        <f>IF(AL50="","",IF(AL50&lt;I50,"不足",IF(AL50&gt;J50,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN50" s="15" t="str"/>
+      <c r="AL50" s="15" t="n">
+        <v>4211</v>
+      </c>
+      <c r="AM50" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN50" s="15" t="inlineStr"/>
       <c r="AO50" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の屋根修理」へリンク。関連：屋根カバー・屋根材注意記事。</t>
@@ -25420,7 +25914,7 @@
       </c>
       <c r="AD51" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE51" s="15" t="inlineStr">
@@ -25430,24 +25924,37 @@
       </c>
       <c r="AF51" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG51" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH51" s="15" t="str"/>
-      <c r="AI51" s="15" t="str"/>
-      <c r="AJ51" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH51" s="15" t="n">
+        <v>22019</v>
+      </c>
+      <c r="AI51" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22019</t>
+        </is>
+      </c>
+      <c r="AJ51" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:15:39</t>
+        </is>
+      </c>
       <c r="AK51" s="69" t="str"/>
-      <c r="AL51" s="15" t="str"/>
-      <c r="AM51" s="15">
-        <f>IF(AL51="","",IF(AL51&lt;I51,"不足",IF(AL51&gt;J51,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN51" s="15" t="str"/>
+      <c r="AL51" s="15" t="n">
+        <v>3806</v>
+      </c>
+      <c r="AM51" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN51" s="15" t="inlineStr"/>
       <c r="AO51" s="15" t="inlineStr">
         <is>
           <t>関連：ベランダ防水費用、シーリング打ち替え費用、外壁雨漏りへリンク。</t>
@@ -25602,7 +26109,7 @@
       </c>
       <c r="AD52" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE52" s="15" t="inlineStr">
@@ -25612,24 +26119,37 @@
       </c>
       <c r="AF52" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG52" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH52" s="15" t="str"/>
-      <c r="AI52" s="15" t="str"/>
-      <c r="AJ52" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH52" s="15" t="n">
+        <v>22021</v>
+      </c>
+      <c r="AI52" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22021</t>
+        </is>
+      </c>
+      <c r="AJ52" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:15:49</t>
+        </is>
+      </c>
       <c r="AK52" s="69" t="str"/>
-      <c r="AL52" s="15" t="str"/>
-      <c r="AM52" s="15">
-        <f>IF(AL52="","",IF(AL52&lt;I52,"不足",IF(AL52&gt;J52,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN52" s="15" t="str"/>
+      <c r="AL52" s="15" t="n">
+        <v>4086</v>
+      </c>
+      <c r="AM52" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN52" s="15" t="inlineStr"/>
       <c r="AO52" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の屋根修理」へリンク。関連：屋根カバー・屋根材注意記事。</t>
@@ -25784,7 +26304,7 @@
       </c>
       <c r="AD53" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE53" s="15" t="inlineStr">
@@ -25794,24 +26314,37 @@
       </c>
       <c r="AF53" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG53" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH53" s="15" t="str"/>
-      <c r="AI53" s="15" t="str"/>
-      <c r="AJ53" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH53" s="15" t="n">
+        <v>22023</v>
+      </c>
+      <c r="AI53" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22023</t>
+        </is>
+      </c>
+      <c r="AJ53" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:15:58</t>
+        </is>
+      </c>
       <c r="AK53" s="69" t="str"/>
-      <c r="AL53" s="15" t="str"/>
-      <c r="AM53" s="15">
-        <f>IF(AL53="","",IF(AL53&lt;I53,"不足",IF(AL53&gt;J53,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN53" s="15" t="str"/>
+      <c r="AL53" s="15" t="n">
+        <v>3710</v>
+      </c>
+      <c r="AM53" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN53" s="15" t="inlineStr"/>
       <c r="AO53" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装工期、足場代、防水工事、屋根カバーへリンク。</t>
@@ -25966,7 +26499,7 @@
       </c>
       <c r="AD54" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE54" s="15" t="inlineStr">
@@ -25976,24 +26509,37 @@
       </c>
       <c r="AF54" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG54" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH54" s="15" t="str"/>
-      <c r="AI54" s="15" t="str"/>
-      <c r="AJ54" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH54" s="15" t="n">
+        <v>22025</v>
+      </c>
+      <c r="AI54" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22025</t>
+        </is>
+      </c>
+      <c r="AJ54" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:16:06</t>
+        </is>
+      </c>
       <c r="AK54" s="69" t="str"/>
-      <c r="AL54" s="15" t="str"/>
-      <c r="AM54" s="15">
-        <f>IF(AL54="","",IF(AL54&lt;I54,"不足",IF(AL54&gt;J54,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN54" s="15" t="str"/>
+      <c r="AL54" s="15" t="n">
+        <v>3705</v>
+      </c>
+      <c r="AM54" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN54" s="15" t="inlineStr"/>
       <c r="AO54" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装工期、足場代、防水工事、屋根カバーへリンク。</t>
@@ -26148,7 +26694,7 @@
       </c>
       <c r="AD55" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE55" s="15" t="inlineStr">
@@ -26158,24 +26704,37 @@
       </c>
       <c r="AF55" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG55" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH55" s="15" t="str"/>
-      <c r="AI55" s="15" t="str"/>
-      <c r="AJ55" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH55" s="15" t="n">
+        <v>22027</v>
+      </c>
+      <c r="AI55" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22027</t>
+        </is>
+      </c>
+      <c r="AJ55" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:16:14</t>
+        </is>
+      </c>
       <c r="AK55" s="69" t="str"/>
-      <c r="AL55" s="15" t="str"/>
-      <c r="AM55" s="15">
-        <f>IF(AL55="","",IF(AL55&lt;I55,"不足",IF(AL55&gt;J55,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN55" s="15" t="str"/>
+      <c r="AL55" s="15" t="n">
+        <v>3707</v>
+      </c>
+      <c r="AM55" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN55" s="15" t="inlineStr"/>
       <c r="AO55" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装工期、足場代、防水工事、屋根カバーへリンク。</t>
@@ -26330,7 +26889,7 @@
       </c>
       <c r="AD56" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE56" s="15" t="inlineStr">
@@ -26340,24 +26899,37 @@
       </c>
       <c r="AF56" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG56" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH56" s="15" t="str"/>
-      <c r="AI56" s="15" t="str"/>
-      <c r="AJ56" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH56" s="15" t="n">
+        <v>22029</v>
+      </c>
+      <c r="AI56" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22029</t>
+        </is>
+      </c>
+      <c r="AJ56" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:16:23</t>
+        </is>
+      </c>
       <c r="AK56" s="69" t="str"/>
-      <c r="AL56" s="15" t="str"/>
-      <c r="AM56" s="15">
-        <f>IF(AL56="","",IF(AL56&lt;I56,"不足",IF(AL56&gt;J56,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN56" s="15" t="str"/>
+      <c r="AL56" s="15" t="n">
+        <v>3687</v>
+      </c>
+      <c r="AM56" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN56" s="15" t="inlineStr"/>
       <c r="AO56" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装工期、足場代、防水工事、屋根カバーへリンク。</t>
@@ -26512,7 +27084,7 @@
       </c>
       <c r="AD57" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE57" s="15" t="inlineStr">
@@ -26522,24 +27094,37 @@
       </c>
       <c r="AF57" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG57" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH57" s="15" t="str"/>
-      <c r="AI57" s="15" t="str"/>
-      <c r="AJ57" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH57" s="15" t="n">
+        <v>22031</v>
+      </c>
+      <c r="AI57" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22031</t>
+        </is>
+      </c>
+      <c r="AJ57" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:16:32</t>
+        </is>
+      </c>
       <c r="AK57" s="69" t="str"/>
-      <c r="AL57" s="15" t="str"/>
-      <c r="AM57" s="15">
-        <f>IF(AL57="","",IF(AL57&lt;I57,"不足",IF(AL57&gt;J57,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN57" s="15" t="str"/>
+      <c r="AL57" s="15" t="n">
+        <v>3684</v>
+      </c>
+      <c r="AM57" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN57" s="15" t="inlineStr"/>
       <c r="AO57" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装工期、足場代、防水工事、屋根カバーへリンク。</t>
@@ -26694,7 +27279,7 @@
       </c>
       <c r="AD58" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE58" s="15" t="inlineStr">
@@ -26704,24 +27289,37 @@
       </c>
       <c r="AF58" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG58" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH58" s="15" t="str"/>
-      <c r="AI58" s="15" t="str"/>
-      <c r="AJ58" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH58" s="15" t="n">
+        <v>22033</v>
+      </c>
+      <c r="AI58" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22033</t>
+        </is>
+      </c>
+      <c r="AJ58" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:16:44</t>
+        </is>
+      </c>
       <c r="AK58" s="69" t="str"/>
-      <c r="AL58" s="15" t="str"/>
-      <c r="AM58" s="15">
-        <f>IF(AL58="","",IF(AL58&lt;I58,"不足",IF(AL58&gt;J58,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN58" s="15" t="str"/>
+      <c r="AL58" s="15" t="n">
+        <v>3695</v>
+      </c>
+      <c r="AM58" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN58" s="15" t="inlineStr"/>
       <c r="AO58" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装工期、足場代、防水工事、屋根カバーへリンク。</t>
@@ -26876,7 +27474,7 @@
       </c>
       <c r="AD59" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE59" s="15" t="inlineStr">
@@ -26886,24 +27484,37 @@
       </c>
       <c r="AF59" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG59" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH59" s="15" t="str"/>
-      <c r="AI59" s="15" t="str"/>
-      <c r="AJ59" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH59" s="15" t="n">
+        <v>22035</v>
+      </c>
+      <c r="AI59" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22035</t>
+        </is>
+      </c>
+      <c r="AJ59" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:16:56</t>
+        </is>
+      </c>
       <c r="AK59" s="69" t="str"/>
-      <c r="AL59" s="15" t="str"/>
-      <c r="AM59" s="15">
-        <f>IF(AL59="","",IF(AL59&lt;I59,"不足",IF(AL59&gt;J59,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN59" s="15" t="str"/>
+      <c r="AL59" s="15" t="n">
+        <v>3687</v>
+      </c>
+      <c r="AM59" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN59" s="15" t="inlineStr"/>
       <c r="AO59" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装工期、足場代、防水工事、屋根カバーへリンク。</t>
@@ -27058,7 +27669,7 @@
       </c>
       <c r="AD60" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE60" s="15" t="inlineStr">
@@ -27068,24 +27679,37 @@
       </c>
       <c r="AF60" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG60" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH60" s="15" t="str"/>
-      <c r="AI60" s="15" t="str"/>
-      <c r="AJ60" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH60" s="15" t="n">
+        <v>22037</v>
+      </c>
+      <c r="AI60" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22037</t>
+        </is>
+      </c>
+      <c r="AJ60" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:17:05</t>
+        </is>
+      </c>
       <c r="AK60" s="69" t="str"/>
-      <c r="AL60" s="15" t="str"/>
-      <c r="AM60" s="15">
-        <f>IF(AL60="","",IF(AL60&lt;I60,"不足",IF(AL60&gt;J60,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN60" s="15" t="str"/>
+      <c r="AL60" s="15" t="n">
+        <v>3627</v>
+      </c>
+      <c r="AM60" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN60" s="15" t="inlineStr"/>
       <c r="AO60" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装工期、足場代、防水工事、屋根カバーへリンク。</t>
@@ -27240,7 +27864,7 @@
       </c>
       <c r="AD61" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE61" s="15" t="inlineStr">
@@ -27250,24 +27874,37 @@
       </c>
       <c r="AF61" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG61" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH61" s="15" t="str"/>
-      <c r="AI61" s="15" t="str"/>
-      <c r="AJ61" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH61" s="15" t="n">
+        <v>22039</v>
+      </c>
+      <c r="AI61" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22039</t>
+        </is>
+      </c>
+      <c r="AJ61" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:17:15</t>
+        </is>
+      </c>
       <c r="AK61" s="69" t="str"/>
-      <c r="AL61" s="15" t="str"/>
-      <c r="AM61" s="15">
-        <f>IF(AL61="","",IF(AL61&lt;I61,"不足",IF(AL61&gt;J61,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN61" s="15" t="str"/>
+      <c r="AL61" s="15" t="n">
+        <v>3643</v>
+      </c>
+      <c r="AM61" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN61" s="15" t="inlineStr"/>
       <c r="AO61" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装工期、足場代、防水工事、屋根カバーへリンク。</t>
@@ -27422,7 +28059,7 @@
       </c>
       <c r="AD62" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE62" s="15" t="inlineStr">
@@ -27432,24 +28069,37 @@
       </c>
       <c r="AF62" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG62" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH62" s="15" t="str"/>
-      <c r="AI62" s="15" t="str"/>
-      <c r="AJ62" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH62" s="15" t="n">
+        <v>22041</v>
+      </c>
+      <c r="AI62" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22041</t>
+        </is>
+      </c>
+      <c r="AJ62" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:17:27</t>
+        </is>
+      </c>
       <c r="AK62" s="69" t="str"/>
-      <c r="AL62" s="15" t="str"/>
-      <c r="AM62" s="15">
-        <f>IF(AL62="","",IF(AL62&lt;I62,"不足",IF(AL62&gt;J62,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN62" s="15" t="str"/>
+      <c r="AL62" s="15" t="n">
+        <v>3756</v>
+      </c>
+      <c r="AM62" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN62" s="15" t="inlineStr"/>
       <c r="AO62" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装、雨樋、軒天、付帯部補修記事へリンク。</t>
@@ -27604,7 +28254,7 @@
       </c>
       <c r="AD63" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE63" s="15" t="inlineStr">
@@ -27614,24 +28264,37 @@
       </c>
       <c r="AF63" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG63" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH63" s="15" t="str"/>
-      <c r="AI63" s="15" t="str"/>
-      <c r="AJ63" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH63" s="15" t="n">
+        <v>22043</v>
+      </c>
+      <c r="AI63" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22043</t>
+        </is>
+      </c>
+      <c r="AJ63" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:17:35</t>
+        </is>
+      </c>
       <c r="AK63" s="69" t="str"/>
-      <c r="AL63" s="15" t="str"/>
-      <c r="AM63" s="15">
-        <f>IF(AL63="","",IF(AL63&lt;I63,"不足",IF(AL63&gt;J63,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN63" s="15" t="str"/>
+      <c r="AL63" s="15" t="n">
+        <v>3753</v>
+      </c>
+      <c r="AM63" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN63" s="15" t="inlineStr"/>
       <c r="AO63" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装、雨樋、軒天、付帯部補修記事へリンク。</t>
@@ -27786,7 +28449,7 @@
       </c>
       <c r="AD64" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE64" s="15" t="inlineStr">
@@ -27796,24 +28459,37 @@
       </c>
       <c r="AF64" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG64" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH64" s="15" t="str"/>
-      <c r="AI64" s="15" t="str"/>
-      <c r="AJ64" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH64" s="15" t="n">
+        <v>22045</v>
+      </c>
+      <c r="AI64" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22045</t>
+        </is>
+      </c>
+      <c r="AJ64" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:17:46</t>
+        </is>
+      </c>
       <c r="AK64" s="69" t="str"/>
-      <c r="AL64" s="15" t="str"/>
-      <c r="AM64" s="15">
-        <f>IF(AL64="","",IF(AL64&lt;I64,"不足",IF(AL64&gt;J64,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN64" s="15" t="str"/>
+      <c r="AL64" s="15" t="n">
+        <v>3285</v>
+      </c>
+      <c r="AM64" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,000〜5,500字)</t>
+        </is>
+      </c>
+      <c r="AN64" s="15" t="inlineStr"/>
       <c r="AO64" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装、雨樋、軒天、付帯部補修記事へリンク。</t>
@@ -27968,7 +28644,7 @@
       </c>
       <c r="AD65" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE65" s="15" t="inlineStr">
@@ -27978,24 +28654,37 @@
       </c>
       <c r="AF65" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG65" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH65" s="15" t="str"/>
-      <c r="AI65" s="15" t="str"/>
-      <c r="AJ65" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH65" s="15" t="n">
+        <v>22047</v>
+      </c>
+      <c r="AI65" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22047</t>
+        </is>
+      </c>
+      <c r="AJ65" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:17:58</t>
+        </is>
+      </c>
       <c r="AK65" s="69" t="str"/>
-      <c r="AL65" s="15" t="str"/>
-      <c r="AM65" s="15">
-        <f>IF(AL65="","",IF(AL65&lt;I65,"不足",IF(AL65&gt;J65,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN65" s="15" t="str"/>
+      <c r="AL65" s="15" t="n">
+        <v>3771</v>
+      </c>
+      <c r="AM65" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN65" s="15" t="inlineStr"/>
       <c r="AO65" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装、雨樋、軒天、付帯部補修記事へリンク。</t>
@@ -28150,7 +28839,7 @@
       </c>
       <c r="AD66" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE66" s="15" t="inlineStr">
@@ -28160,24 +28849,37 @@
       </c>
       <c r="AF66" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG66" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH66" s="15" t="str"/>
-      <c r="AI66" s="15" t="str"/>
-      <c r="AJ66" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH66" s="15" t="n">
+        <v>22049</v>
+      </c>
+      <c r="AI66" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22049</t>
+        </is>
+      </c>
+      <c r="AJ66" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:18:08</t>
+        </is>
+      </c>
       <c r="AK66" s="69" t="str"/>
-      <c r="AL66" s="15" t="str"/>
-      <c r="AM66" s="15">
-        <f>IF(AL66="","",IF(AL66&lt;I66,"不足",IF(AL66&gt;J66,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN66" s="15" t="str"/>
+      <c r="AL66" s="15" t="n">
+        <v>3764</v>
+      </c>
+      <c r="AM66" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN66" s="15" t="inlineStr"/>
       <c r="AO66" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装、雨樋、軒天、付帯部補修記事へリンク。</t>
@@ -28332,7 +29034,7 @@
       </c>
       <c r="AD67" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE67" s="15" t="inlineStr">
@@ -28342,24 +29044,37 @@
       </c>
       <c r="AF67" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG67" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH67" s="15" t="str"/>
-      <c r="AI67" s="15" t="str"/>
-      <c r="AJ67" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH67" s="15" t="n">
+        <v>22051</v>
+      </c>
+      <c r="AI67" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22051</t>
+        </is>
+      </c>
+      <c r="AJ67" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:18:17</t>
+        </is>
+      </c>
       <c r="AK67" s="69" t="str"/>
-      <c r="AL67" s="15" t="str"/>
-      <c r="AM67" s="15">
-        <f>IF(AL67="","",IF(AL67&lt;I67,"不足",IF(AL67&gt;J67,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN67" s="15" t="str"/>
+      <c r="AL67" s="15" t="n">
+        <v>3762</v>
+      </c>
+      <c r="AM67" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN67" s="15" t="inlineStr"/>
       <c r="AO67" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装、雨樋、軒天、付帯部補修記事へリンク。</t>
@@ -28514,7 +29229,7 @@
       </c>
       <c r="AD68" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE68" s="15" t="inlineStr">
@@ -28524,24 +29239,37 @@
       </c>
       <c r="AF68" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG68" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH68" s="15" t="str"/>
-      <c r="AI68" s="15" t="str"/>
-      <c r="AJ68" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH68" s="15" t="n">
+        <v>22053</v>
+      </c>
+      <c r="AI68" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22053</t>
+        </is>
+      </c>
+      <c r="AJ68" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:18:27</t>
+        </is>
+      </c>
       <c r="AK68" s="69" t="str"/>
-      <c r="AL68" s="15" t="str"/>
-      <c r="AM68" s="15">
-        <f>IF(AL68="","",IF(AL68&lt;I68,"不足",IF(AL68&gt;J68,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN68" s="15" t="str"/>
+      <c r="AL68" s="15" t="n">
+        <v>3752</v>
+      </c>
+      <c r="AM68" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN68" s="15" t="inlineStr"/>
       <c r="AO68" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装、雨樋、軒天、付帯部補修記事へリンク。</t>
@@ -28696,7 +29424,7 @@
       </c>
       <c r="AD69" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE69" s="15" t="inlineStr">
@@ -28706,24 +29434,37 @@
       </c>
       <c r="AF69" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG69" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH69" s="15" t="str"/>
-      <c r="AI69" s="15" t="str"/>
-      <c r="AJ69" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH69" s="15" t="n">
+        <v>22055</v>
+      </c>
+      <c r="AI69" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22055</t>
+        </is>
+      </c>
+      <c r="AJ69" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:18:34</t>
+        </is>
+      </c>
       <c r="AK69" s="69" t="str"/>
-      <c r="AL69" s="15" t="str"/>
-      <c r="AM69" s="15">
-        <f>IF(AL69="","",IF(AL69&lt;I69,"不足",IF(AL69&gt;J69,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN69" s="15" t="str"/>
+      <c r="AL69" s="15" t="n">
+        <v>3761</v>
+      </c>
+      <c r="AM69" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN69" s="15" t="inlineStr"/>
       <c r="AO69" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装、雨樋、軒天、付帯部補修記事へリンク。</t>
@@ -28878,7 +29619,7 @@
       </c>
       <c r="AD70" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE70" s="15" t="inlineStr">
@@ -28888,24 +29629,37 @@
       </c>
       <c r="AF70" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG70" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH70" s="15" t="str"/>
-      <c r="AI70" s="15" t="str"/>
-      <c r="AJ70" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH70" s="15" t="n">
+        <v>22057</v>
+      </c>
+      <c r="AI70" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22057</t>
+        </is>
+      </c>
+      <c r="AJ70" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:18:44</t>
+        </is>
+      </c>
       <c r="AK70" s="69" t="str"/>
-      <c r="AL70" s="15" t="str"/>
-      <c r="AM70" s="15">
-        <f>IF(AL70="","",IF(AL70&lt;I70,"不足",IF(AL70&gt;J70,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN70" s="15" t="str"/>
+      <c r="AL70" s="15" t="n">
+        <v>3314</v>
+      </c>
+      <c r="AM70" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,000〜5,500字)</t>
+        </is>
+      </c>
+      <c r="AN70" s="15" t="inlineStr"/>
       <c r="AO70" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装、雨樋、軒天、付帯部補修記事へリンク。</t>
@@ -29060,7 +29814,7 @@
       </c>
       <c r="AD71" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE71" s="15" t="inlineStr">
@@ -29070,24 +29824,37 @@
       </c>
       <c r="AF71" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG71" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH71" s="15" t="str"/>
-      <c r="AI71" s="15" t="str"/>
-      <c r="AJ71" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH71" s="15" t="n">
+        <v>22059</v>
+      </c>
+      <c r="AI71" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22059</t>
+        </is>
+      </c>
+      <c r="AJ71" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:18:53</t>
+        </is>
+      </c>
       <c r="AK71" s="69" t="str"/>
-      <c r="AL71" s="15" t="str"/>
-      <c r="AM71" s="15">
-        <f>IF(AL71="","",IF(AL71&lt;I71,"不足",IF(AL71&gt;J71,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN71" s="15" t="str"/>
+      <c r="AL71" s="15" t="n">
+        <v>3791</v>
+      </c>
+      <c r="AM71" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN71" s="15" t="inlineStr"/>
       <c r="AO71" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装、雨樋、軒天、付帯部補修記事へリンク。</t>

--- a/data/seo_80kw_production_management_v2_with_image_prompt_sheet.xlsx
+++ b/data/seo_80kw_production_management_v2_with_image_prompt_sheet.xlsx
@@ -24367,7 +24367,7 @@
       </c>
       <c r="AD43" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE43" s="15" t="inlineStr">
@@ -24377,24 +24377,37 @@
       </c>
       <c r="AF43" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG43" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH43" s="15" t="str"/>
-      <c r="AI43" s="15" t="str"/>
-      <c r="AJ43" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH43" s="15" t="n">
+        <v>22066</v>
+      </c>
+      <c r="AI43" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22066</t>
+        </is>
+      </c>
+      <c r="AJ43" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-28 10:55:44</t>
+        </is>
+      </c>
       <c r="AK43" s="69" t="str"/>
-      <c r="AL43" s="15" t="str"/>
-      <c r="AM43" s="15">
-        <f>IF(AL43="","",IF(AL43&lt;I43,"不足",IF(AL43&gt;J43,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN43" s="15" t="str"/>
+      <c r="AL43" s="15" t="n">
+        <v>4171</v>
+      </c>
+      <c r="AM43" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安5,000〜7,000字)</t>
+        </is>
+      </c>
+      <c r="AN43" s="15" t="inlineStr"/>
       <c r="AO43" s="15" t="inlineStr">
         <is>
           <t>中心記事「松山市の屋根修理」へリンク。関連：屋根カバー・屋根材注意記事。</t>
@@ -30009,7 +30022,7 @@
       </c>
       <c r="AD72" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE72" s="15" t="inlineStr">
@@ -30019,24 +30032,37 @@
       </c>
       <c r="AF72" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG72" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH72" s="15" t="str"/>
-      <c r="AI72" s="15" t="str"/>
-      <c r="AJ72" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH72" s="15" t="n">
+        <v>22068</v>
+      </c>
+      <c r="AI72" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22068</t>
+        </is>
+      </c>
+      <c r="AJ72" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-28 10:55:55</t>
+        </is>
+      </c>
       <c r="AK72" s="69" t="str"/>
-      <c r="AL72" s="15" t="str"/>
-      <c r="AM72" s="15">
-        <f>IF(AL72="","",IF(AL72&lt;I72,"不足",IF(AL72&gt;J72,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN72" s="15" t="str"/>
+      <c r="AL72" s="15" t="n">
+        <v>3551</v>
+      </c>
+      <c r="AM72" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN72" s="15" t="inlineStr"/>
       <c r="AO72" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装、雨樋、軒天、付帯部補修記事へリンク。</t>
@@ -30191,7 +30217,7 @@
       </c>
       <c r="AD73" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE73" s="15" t="inlineStr">
@@ -30201,24 +30227,37 @@
       </c>
       <c r="AF73" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG73" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH73" s="15" t="str"/>
-      <c r="AI73" s="15" t="str"/>
-      <c r="AJ73" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH73" s="15" t="n">
+        <v>22070</v>
+      </c>
+      <c r="AI73" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22070</t>
+        </is>
+      </c>
+      <c r="AJ73" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-28 10:56:04</t>
+        </is>
+      </c>
       <c r="AK73" s="69" t="str"/>
-      <c r="AL73" s="15" t="str"/>
-      <c r="AM73" s="15">
-        <f>IF(AL73="","",IF(AL73&lt;I73,"不足",IF(AL73&gt;J73,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN73" s="15" t="str"/>
+      <c r="AL73" s="15" t="n">
+        <v>3553</v>
+      </c>
+      <c r="AM73" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN73" s="15" t="inlineStr"/>
       <c r="AO73" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装、雨樋、軒天、付帯部補修記事へリンク。</t>
@@ -30373,7 +30412,7 @@
       </c>
       <c r="AD74" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE74" s="15" t="inlineStr">
@@ -30383,24 +30422,37 @@
       </c>
       <c r="AF74" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG74" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH74" s="15" t="str"/>
-      <c r="AI74" s="15" t="str"/>
-      <c r="AJ74" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH74" s="15" t="n">
+        <v>22072</v>
+      </c>
+      <c r="AI74" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22072</t>
+        </is>
+      </c>
+      <c r="AJ74" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-28 10:56:13</t>
+        </is>
+      </c>
       <c r="AK74" s="69" t="str"/>
-      <c r="AL74" s="15" t="str"/>
-      <c r="AM74" s="15">
-        <f>IF(AL74="","",IF(AL74&lt;I74,"不足",IF(AL74&gt;J74,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN74" s="15" t="str"/>
+      <c r="AL74" s="15" t="n">
+        <v>3237</v>
+      </c>
+      <c r="AM74" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,000〜5,500字)</t>
+        </is>
+      </c>
+      <c r="AN74" s="15" t="inlineStr"/>
       <c r="AO74" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装、雨樋、軒天、付帯部補修記事へリンク。</t>
@@ -30555,7 +30607,7 @@
       </c>
       <c r="AD75" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE75" s="15" t="inlineStr">
@@ -30565,24 +30617,37 @@
       </c>
       <c r="AF75" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG75" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH75" s="15" t="str"/>
-      <c r="AI75" s="15" t="str"/>
-      <c r="AJ75" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH75" s="15" t="n">
+        <v>22074</v>
+      </c>
+      <c r="AI75" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22074</t>
+        </is>
+      </c>
+      <c r="AJ75" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-28 10:56:23</t>
+        </is>
+      </c>
       <c r="AK75" s="69" t="str"/>
-      <c r="AL75" s="15" t="str"/>
-      <c r="AM75" s="15">
-        <f>IF(AL75="","",IF(AL75&lt;I75,"不足",IF(AL75&gt;J75,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN75" s="15" t="str"/>
+      <c r="AL75" s="15" t="n">
+        <v>3228</v>
+      </c>
+      <c r="AM75" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,000〜5,500字)</t>
+        </is>
+      </c>
+      <c r="AN75" s="15" t="inlineStr"/>
       <c r="AO75" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装、雨樋、軒天、付帯部補修記事へリンク。</t>
@@ -30737,7 +30802,7 @@
       </c>
       <c r="AD76" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE76" s="15" t="inlineStr">
@@ -30747,24 +30812,37 @@
       </c>
       <c r="AF76" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG76" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH76" s="15" t="str"/>
-      <c r="AI76" s="15" t="str"/>
-      <c r="AJ76" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH76" s="15" t="n">
+        <v>22076</v>
+      </c>
+      <c r="AI76" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22076</t>
+        </is>
+      </c>
+      <c r="AJ76" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-28 10:56:33</t>
+        </is>
+      </c>
       <c r="AK76" s="69" t="str"/>
-      <c r="AL76" s="15" t="str"/>
-      <c r="AM76" s="15">
-        <f>IF(AL76="","",IF(AL76&lt;I76,"不足",IF(AL76&gt;J76,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN76" s="15" t="str"/>
+      <c r="AL76" s="15" t="n">
+        <v>3552</v>
+      </c>
+      <c r="AM76" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN76" s="15" t="inlineStr"/>
       <c r="AO76" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装、雨樋、軒天、付帯部補修記事へリンク。</t>
@@ -30919,7 +30997,7 @@
       </c>
       <c r="AD77" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE77" s="15" t="inlineStr">
@@ -30929,24 +31007,37 @@
       </c>
       <c r="AF77" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG77" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH77" s="15" t="str"/>
-      <c r="AI77" s="15" t="str"/>
-      <c r="AJ77" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH77" s="15" t="n">
+        <v>22079</v>
+      </c>
+      <c r="AI77" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22079</t>
+        </is>
+      </c>
+      <c r="AJ77" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-28 10:56:46</t>
+        </is>
+      </c>
       <c r="AK77" s="69" t="str"/>
-      <c r="AL77" s="15" t="str"/>
-      <c r="AM77" s="15">
-        <f>IF(AL77="","",IF(AL77&lt;I77,"不足",IF(AL77&gt;J77,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN77" s="15" t="str"/>
+      <c r="AL77" s="15" t="n">
+        <v>3568</v>
+      </c>
+      <c r="AM77" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN77" s="15" t="inlineStr"/>
       <c r="AO77" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装、雨樋、軒天、付帯部補修記事へリンク。</t>
@@ -31101,7 +31192,7 @@
       </c>
       <c r="AD78" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE78" s="15" t="inlineStr">
@@ -31111,24 +31202,37 @@
       </c>
       <c r="AF78" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="AG78" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH78" s="15" t="str"/>
-      <c r="AI78" s="15" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH78" s="15" t="n">
+        <v>21983</v>
+      </c>
+      <c r="AI78" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=21983</t>
+        </is>
+      </c>
       <c r="AJ78" s="69" t="str"/>
       <c r="AK78" s="69" t="str"/>
-      <c r="AL78" s="15" t="str"/>
-      <c r="AM78" s="15">
-        <f>IF(AL78="","",IF(AL78&lt;I78,"不足",IF(AL78&gt;J78,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN78" s="15" t="str"/>
+      <c r="AL78" s="15" t="n">
+        <v>3551</v>
+      </c>
+      <c r="AM78" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN78" s="15" t="inlineStr">
+        <is>
+          <t>同一 slug の投稿が既に存在するためスキップ（更新するには write_mode=update_only/upsert）</t>
+        </is>
+      </c>
       <c r="AO78" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装、雨樋、軒天、付帯部補修記事へリンク。</t>
@@ -31283,7 +31387,7 @@
       </c>
       <c r="AD79" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE79" s="15" t="inlineStr">
@@ -31293,24 +31397,37 @@
       </c>
       <c r="AF79" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG79" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH79" s="15" t="str"/>
-      <c r="AI79" s="15" t="str"/>
-      <c r="AJ79" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH79" s="15" t="n">
+        <v>22081</v>
+      </c>
+      <c r="AI79" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22081</t>
+        </is>
+      </c>
+      <c r="AJ79" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-28 10:56:57</t>
+        </is>
+      </c>
       <c r="AK79" s="69" t="str"/>
-      <c r="AL79" s="15" t="str"/>
-      <c r="AM79" s="15">
-        <f>IF(AL79="","",IF(AL79&lt;I79,"不足",IF(AL79&gt;J79,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN79" s="15" t="str"/>
+      <c r="AL79" s="15" t="n">
+        <v>3554</v>
+      </c>
+      <c r="AM79" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN79" s="15" t="inlineStr"/>
       <c r="AO79" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装、雨樋、軒天、付帯部補修記事へリンク。</t>
@@ -31465,7 +31582,7 @@
       </c>
       <c r="AD80" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE80" s="15" t="inlineStr">
@@ -31475,24 +31592,37 @@
       </c>
       <c r="AF80" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG80" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH80" s="15" t="str"/>
-      <c r="AI80" s="15" t="str"/>
-      <c r="AJ80" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH80" s="15" t="n">
+        <v>22083</v>
+      </c>
+      <c r="AI80" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22083</t>
+        </is>
+      </c>
+      <c r="AJ80" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-28 10:57:07</t>
+        </is>
+      </c>
       <c r="AK80" s="69" t="str"/>
-      <c r="AL80" s="15" t="str"/>
-      <c r="AM80" s="15">
-        <f>IF(AL80="","",IF(AL80&lt;I80,"不足",IF(AL80&gt;J80,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN80" s="15" t="str"/>
+      <c r="AL80" s="15" t="n">
+        <v>3554</v>
+      </c>
+      <c r="AM80" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN80" s="15" t="inlineStr"/>
       <c r="AO80" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装、雨樋、軒天、付帯部補修記事へリンク。</t>
@@ -31647,7 +31777,7 @@
       </c>
       <c r="AD81" s="15" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>画像確認済み</t>
         </is>
       </c>
       <c r="AE81" s="15" t="inlineStr">
@@ -31657,24 +31787,37 @@
       </c>
       <c r="AF81" s="15" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>posted</t>
         </is>
       </c>
       <c r="AG81" s="15" t="inlineStr">
         <is>
-          <t>create_only</t>
-        </is>
-      </c>
-      <c r="AH81" s="15" t="str"/>
-      <c r="AI81" s="15" t="str"/>
-      <c r="AJ81" s="69" t="str"/>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH81" s="15" t="n">
+        <v>22085</v>
+      </c>
+      <c r="AI81" s="15" t="inlineStr">
+        <is>
+          <t>https://www.sunadatosou.com/?p=22085</t>
+        </is>
+      </c>
+      <c r="AJ81" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-28 10:57:17</t>
+        </is>
+      </c>
       <c r="AK81" s="69" t="str"/>
-      <c r="AL81" s="15" t="str"/>
-      <c r="AM81" s="15">
-        <f>IF(AL81="","",IF(AL81&lt;I81,"不足",IF(AL81&gt;J81,"超過","OK")))</f>
-        <v/>
-      </c>
-      <c r="AN81" s="15" t="str"/>
+      <c r="AL81" s="15" t="n">
+        <v>3567</v>
+      </c>
+      <c r="AM81" s="15" t="inlineStr">
+        <is>
+          <t>不足(目安4,500〜6,000字)</t>
+        </is>
+      </c>
+      <c r="AN81" s="15" t="inlineStr"/>
       <c r="AO81" s="15" t="inlineStr">
         <is>
           <t>関連：外壁塗装、雨樋、軒天、付帯部補修記事へリンク。</t>

--- a/data/seo_80kw_production_management_v2_with_image_prompt_sheet.xlsx
+++ b/data/seo_80kw_production_management_v2_with_image_prompt_sheet.xlsx
@@ -31209,12 +31209,12 @@
       </c>
       <c r="AF78" s="5" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>updated</t>
         </is>
       </c>
       <c r="AG78" s="5" t="inlineStr">
         <is>
-          <t>post/create_only</t>
+          <t>post/update_only</t>
         </is>
       </c>
       <c r="AH78" s="5" t="n">
@@ -31226,7 +31226,11 @@
         </is>
       </c>
       <c r="AJ78" s="29" t="n"/>
-      <c r="AK78" s="29" t="n"/>
+      <c r="AK78" s="29" t="inlineStr">
+        <is>
+          <t>2026-06-28 11:24:08</t>
+        </is>
+      </c>
       <c r="AL78" s="5" t="n">
         <v>3551</v>
       </c>
@@ -31235,11 +31239,7 @@
           <t>不足(目安4,500〜6,000字)</t>
         </is>
       </c>
-      <c r="AN78" s="5" t="inlineStr">
-        <is>
-          <t>同一 slug の投稿が既に存在するためスキップ（更新するには write_mode=update_only/upsert）</t>
-        </is>
-      </c>
+      <c r="AN78" s="5" t="inlineStr"/>
       <c r="AO78" s="5" t="inlineStr">
         <is>
           <t>関連：外壁塗装、雨樋、軒天、付帯部補修記事へリンク。</t>

--- a/data/seo_80kw_production_management_v2_with_image_prompt_sheet.xlsx
+++ b/data/seo_80kw_production_management_v2_with_image_prompt_sheet.xlsx
@@ -31124,7 +31124,7 @@
       </c>
       <c r="O78" s="5" t="inlineStr">
         <is>
-          <t>soffit-leak</t>
+          <t>soffit-leak-cause</t>
         </is>
       </c>
       <c r="P78" s="5" t="inlineStr">
